--- a/straight_redis_client/profiling/redis_client_profiling.xlsx
+++ b/straight_redis_client/profiling/redis_client_profiling.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\straight_redis_client\profiling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3EA393-E696-4DDC-AE96-49158903691E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7929C4AC-9FE9-49CA-88D4-482E78CC2442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ping" sheetId="1" r:id="rId1"/>
     <sheet name="set" sheetId="9" r:id="rId2"/>
     <sheet name="get" sheetId="3" r:id="rId3"/>
     <sheet name="get_range" sheetId="4" r:id="rId4"/>
-    <sheet name="del_keys" sheetId="5" r:id="rId5"/>
+    <sheet name="delete" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="20">
   <si>
     <t>Client: Local</t>
   </si>
@@ -606,9 +606,7 @@
       <c r="B6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
-      </c>
+      <c r="C6" s="14"/>
       <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -618,9 +616,7 @@
       <c r="B7" s="18">
         <v>2.3041500011458898E-3</v>
       </c>
-      <c r="C7" s="18">
-        <v>0</v>
-      </c>
+      <c r="C7" s="18"/>
       <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -630,9 +626,7 @@
       <c r="B8" s="18">
         <v>1.8066439998801798E-2</v>
       </c>
-      <c r="C8" s="18">
-        <v>0</v>
-      </c>
+      <c r="C8" s="18"/>
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -642,9 +636,7 @@
       <c r="B9" s="16">
         <v>0.17748495001578701</v>
       </c>
-      <c r="C9" s="16">
-        <v>0</v>
-      </c>
+      <c r="C9" s="16"/>
       <c r="D9" s="8"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -657,9 +649,7 @@
       <c r="B10" s="16">
         <v>1.85243663000874</v>
       </c>
-      <c r="C10" s="16">
-        <v>0</v>
-      </c>
+      <c r="C10" s="16"/>
       <c r="D10" s="10"/>
       <c r="H10" s="7"/>
     </row>
@@ -1455,7 +1445,7 @@
         <v>2.1452300250530201E-3</v>
       </c>
       <c r="C7" s="18">
-        <v>0</v>
+        <v>2.4343300028704098E-3</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>11</v>
@@ -1469,7 +1459,7 @@
         <v>2.49298300012014E-2</v>
       </c>
       <c r="C8" s="18">
-        <v>0</v>
+        <v>2.5533499894663599E-3</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>10</v>
@@ -1483,7 +1473,7 @@
         <v>0.22794040001463101</v>
       </c>
       <c r="C9" s="16">
-        <v>0</v>
+        <v>5.1798400003463E-3</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>10</v>
@@ -1500,7 +1490,7 @@
         <v>2.2695505899959199</v>
       </c>
       <c r="C10" s="16">
-        <v>0</v>
+        <v>2.3080520005896599E-2</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>10</v>
@@ -1876,7 +1866,7 @@
         <v>2.00985999545082E-3</v>
       </c>
       <c r="C7" s="18">
-        <v>0</v>
+        <v>2.9287799960002301E-3</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>12</v>
@@ -1890,7 +1880,7 @@
         <v>1.7116870009340299E-2</v>
       </c>
       <c r="C8" s="18">
-        <v>0</v>
+        <v>3.8782599964178998E-3</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>12</v>
@@ -1904,7 +1894,7 @@
         <v>0.19453054998302799</v>
       </c>
       <c r="C9" s="16">
-        <v>0</v>
+        <v>5.8791999937966403E-3</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>12</v>
@@ -1921,7 +1911,7 @@
         <v>2.1778757099993502</v>
       </c>
       <c r="C10" s="16">
-        <v>0</v>
+        <v>2.5481500010937401E-2</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>12</v>
@@ -2297,7 +2287,7 @@
         <v>1.7936599999666201E-2</v>
       </c>
       <c r="C7" s="18">
-        <v>0</v>
+        <v>2.2126199910417199E-3</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>13</v>
@@ -2311,7 +2301,7 @@
         <v>1.9478040002286399E-2</v>
       </c>
       <c r="C8" s="18">
-        <v>0</v>
+        <v>6.3647500122897297E-3</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>13</v>
@@ -2325,7 +2315,7 @@
         <v>0.20511929001659099</v>
       </c>
       <c r="C9" s="16">
-        <v>0</v>
+        <v>9.5526600140146897E-3</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>13</v>
@@ -2342,7 +2332,7 @@
         <v>2.0944676799932398</v>
       </c>
       <c r="C10" s="16">
-        <v>0</v>
+        <v>1.7872149986214898E-2</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>13</v>

--- a/straight_redis_client/profiling/redis_client_profiling.xlsx
+++ b/straight_redis_client/profiling/redis_client_profiling.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\straight_redis_client\profiling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7929C4AC-9FE9-49CA-88D4-482E78CC2442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F79BF4-3682-4055-AE6D-91518952F628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ping" sheetId="1" r:id="rId1"/>
-    <sheet name="set" sheetId="9" r:id="rId2"/>
-    <sheet name="get" sheetId="3" r:id="rId3"/>
-    <sheet name="get_range" sheetId="4" r:id="rId4"/>
-    <sheet name="delete" sheetId="5" r:id="rId5"/>
+    <sheet name="Ping Message" sheetId="1" r:id="rId1"/>
+    <sheet name="Set Function" sheetId="9" r:id="rId2"/>
+    <sheet name="Get Function" sheetId="3" r:id="rId3"/>
+    <sheet name="Get-Range Function" sheetId="4" r:id="rId4"/>
+    <sheet name="Delete Function" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -33,9 +33,6 @@
   </si>
   <si>
     <t>Client_Instances=1</t>
-  </si>
-  <si>
-    <t>Wall_Time(seconds)</t>
   </si>
   <si>
     <t>Wall Time: Time taken from sending the response and receiving the response back</t>
@@ -74,9 +71,6 @@
     <t>Redis_DB=10.0.2.82:6379</t>
   </si>
   <si>
-    <t>Wall_Time_Optimized(seconds)</t>
-  </si>
-  <si>
     <t>Optimized with pipeline operators</t>
   </si>
   <si>
@@ -84,6 +78,12 @@
   </si>
   <si>
     <t>Throughput(Number_of_Key_Value_Pairs)</t>
+  </si>
+  <si>
+    <t>Response_Time (seconds)</t>
+  </si>
+  <si>
+    <t>Response_Time_Optimized (seconds)</t>
   </si>
 </sst>
 </file>
@@ -582,13 +582,13 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -601,10 +601,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>3</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="12"/>
@@ -702,7 +702,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -747,12 +747,12 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="5"/>
     </row>
@@ -979,13 +979,13 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -998,21 +998,21 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -1026,7 +1026,7 @@
         <v>2.9214599984697998E-3</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1040,7 +1040,7 @@
         <v>2.9676700010895698E-3</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1054,7 +1054,7 @@
         <v>4.7610499896109104E-3</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -1071,7 +1071,7 @@
         <v>2.6601759984623601E-2</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1169,12 +1169,12 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="5"/>
     </row>
@@ -1401,13 +1401,13 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -1420,21 +1420,21 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -1448,7 +1448,7 @@
         <v>2.4343300028704098E-3</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1462,7 +1462,7 @@
         <v>2.5533499894663599E-3</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1476,7 +1476,7 @@
         <v>5.1798400003463E-3</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -1493,7 +1493,7 @@
         <v>2.3080520005896599E-2</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1591,12 +1591,12 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="5"/>
     </row>
@@ -1822,13 +1822,13 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -1841,21 +1841,21 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -1869,7 +1869,7 @@
         <v>2.9287799960002301E-3</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1883,7 +1883,7 @@
         <v>3.8782599964178998E-3</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1897,7 +1897,7 @@
         <v>5.8791999937966403E-3</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -1914,7 +1914,7 @@
         <v>2.5481500010937401E-2</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2012,12 +2012,12 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="5"/>
     </row>
@@ -2243,13 +2243,13 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -2262,21 +2262,21 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>2.2126199910417199E-3</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2304,7 +2304,7 @@
         <v>6.3647500122897297E-3</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2318,7 +2318,7 @@
         <v>9.5526600140146897E-3</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
@@ -2335,7 +2335,7 @@
         <v>1.7872149986214898E-2</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2433,12 +2433,12 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="5"/>
     </row>

--- a/straight_redis_client/profiling/redis_client_profiling.xlsx
+++ b/straight_redis_client/profiling/redis_client_profiling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\straight_redis_client\profiling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F79BF4-3682-4055-AE6D-91518952F628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1723247-6E52-4C7D-A742-B21470BC924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ping Message" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
     <sheet name="Get-Range Function" sheetId="4" r:id="rId4"/>
     <sheet name="Delete Function" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2301,7 +2314,7 @@
         <v>1.9478040002286399E-2</v>
       </c>
       <c r="C8" s="18">
-        <v>6.3647500122897297E-3</v>
+        <v>2.9057799984002399E-3</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>12</v>
@@ -2315,7 +2328,7 @@
         <v>0.20511929001659099</v>
       </c>
       <c r="C9" s="16">
-        <v>9.5526600140146897E-3</v>
+        <v>4.2851400037761701E-3</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>12</v>
@@ -2332,7 +2345,7 @@
         <v>2.0944676799932398</v>
       </c>
       <c r="C10" s="16">
-        <v>1.7872149986214898E-2</v>
+        <v>1.4965470001334301E-2</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>12</v>

--- a/straight_redis_client/profiling/redis_client_profiling.xlsx
+++ b/straight_redis_client/profiling/redis_client_profiling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\straight_redis_client\profiling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1723247-6E52-4C7D-A742-B21470BC924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382E39CB-F9D9-4377-B927-1AC79CBE8B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="29040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ping Message" sheetId="1" r:id="rId1"/>

--- a/straight_redis_client/profiling/redis_client_profiling.xlsx
+++ b/straight_redis_client/profiling/redis_client_profiling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\straight_redis_client\profiling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382E39CB-F9D9-4377-B927-1AC79CBE8B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC18E87E-FE48-4598-94B7-F3158B729D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ping Message" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="21">
   <si>
     <t>Client: Local</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Response_Time_Optimized (seconds)</t>
+  </si>
+  <si>
+    <t>Response_Time(ms)</t>
   </si>
 </sst>
 </file>
@@ -238,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -269,6 +272,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -980,7 +989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349D7314-AB8E-4AA0-A861-31CE52CA3EE8}">
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -990,7 +999,7 @@
     <col min="5" max="5" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1004,17 +1013,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>17</v>
       </c>
@@ -1024,11 +1033,14 @@
       <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>1</v>
       </c>
@@ -1038,11 +1050,15 @@
       <c r="C7" s="18">
         <v>2.9214599984697998E-3</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25">
+        <f>C7*1000</f>
+        <v>2.9214599984697998</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>10</v>
       </c>
@@ -1052,11 +1068,15 @@
       <c r="C8" s="18">
         <v>2.9676700010895698E-3</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="25">
+        <f t="shared" ref="D8:D10" si="0">C8*1000</f>
+        <v>2.9676700010895698</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>100</v>
       </c>
@@ -1066,14 +1086,18 @@
       <c r="C9" s="16">
         <v>4.7610499896109104E-3</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="25">
+        <f t="shared" si="0"/>
+        <v>4.7610499896109104</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="7"/>
       <c r="J9" s="7"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K9" s="7"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>1000</v>
       </c>
@@ -1083,44 +1107,53 @@
       <c r="C10" s="16">
         <v>2.6601759984623601E-2</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="25">
+        <f t="shared" si="0"/>
+        <v>26.601759984623602</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D11" s="26"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="20"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D12" s="26"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D13" s="26"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="26"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D15" s="27"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1402,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -1412,7 +1445,7 @@
     <col min="5" max="5" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1426,17 +1459,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>17</v>
       </c>
@@ -1446,11 +1479,14 @@
       <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>1</v>
       </c>
@@ -1460,11 +1496,15 @@
       <c r="C7" s="18">
         <v>2.4343300028704098E-3</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25">
+        <f>C7*1000</f>
+        <v>2.4343300028704098</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>10</v>
       </c>
@@ -1474,11 +1514,15 @@
       <c r="C8" s="18">
         <v>2.5533499894663599E-3</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="25">
+        <f t="shared" ref="D8:D10" si="0">C8*1000</f>
+        <v>2.5533499894663598</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>100</v>
       </c>
@@ -1488,14 +1532,18 @@
       <c r="C9" s="16">
         <v>5.1798400003463E-3</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="25">
+        <f t="shared" si="0"/>
+        <v>5.1798400003463003</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="7"/>
       <c r="J9" s="7"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K9" s="7"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>1000</v>
       </c>
@@ -1505,44 +1553,53 @@
       <c r="C10" s="16">
         <v>2.3080520005896599E-2</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="25">
+        <f t="shared" si="0"/>
+        <v>23.080520005896599</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D11" s="26"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="20"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D12" s="26"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D13" s="26"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="26"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D15" s="27"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1823,7 +1880,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -1833,7 +1890,7 @@
     <col min="5" max="5" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1847,17 +1904,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>17</v>
       </c>
@@ -1867,11 +1924,14 @@
       <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>1</v>
       </c>
@@ -1881,11 +1941,15 @@
       <c r="C7" s="18">
         <v>2.9287799960002301E-3</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25">
+        <f>C7*1000</f>
+        <v>2.9287799960002299</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>10</v>
       </c>
@@ -1895,11 +1959,15 @@
       <c r="C8" s="18">
         <v>3.8782599964178998E-3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="25">
+        <f t="shared" ref="D8:D10" si="0">C8*1000</f>
+        <v>3.8782599964178996</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>100</v>
       </c>
@@ -1909,14 +1977,18 @@
       <c r="C9" s="16">
         <v>5.8791999937966403E-3</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="25">
+        <f t="shared" si="0"/>
+        <v>5.8791999937966404</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="7"/>
       <c r="J9" s="7"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K9" s="7"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>1000</v>
       </c>
@@ -1926,44 +1998,53 @@
       <c r="C10" s="16">
         <v>2.5481500010937401E-2</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="25">
+        <f t="shared" si="0"/>
+        <v>25.481500010937403</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D11" s="26"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="20"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D12" s="26"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D13" s="26"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="26"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D15" s="27"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2244,7 +2325,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -2254,7 +2335,7 @@
     <col min="5" max="5" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -2268,17 +2349,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>17</v>
       </c>
@@ -2288,11 +2369,14 @@
       <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>1</v>
       </c>
@@ -2302,11 +2386,15 @@
       <c r="C7" s="18">
         <v>2.2126199910417199E-3</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25">
+        <f>C7*1000</f>
+        <v>2.2126199910417199</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>10</v>
       </c>
@@ -2316,11 +2404,15 @@
       <c r="C8" s="18">
         <v>2.9057799984002399E-3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="25">
+        <f t="shared" ref="D8:D10" si="0">C8*1000</f>
+        <v>2.9057799984002397</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>100</v>
       </c>
@@ -2330,14 +2422,18 @@
       <c r="C9" s="16">
         <v>4.2851400037761701E-3</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="25">
+        <f t="shared" si="0"/>
+        <v>4.2851400037761698</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="7"/>
       <c r="J9" s="7"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K9" s="7"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>1000</v>
       </c>
@@ -2347,44 +2443,53 @@
       <c r="C10" s="16">
         <v>1.4965470001334301E-2</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="25">
+        <f t="shared" si="0"/>
+        <v>14.965470001334301</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D11" s="26"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="20"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D12" s="26"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D13" s="26"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="26"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D15" s="27"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
